--- a/diseases/d045/2000-2004.xlsx
+++ b/diseases/d045/2000-2004.xlsx
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24397,7 +24397,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28213,7 +28213,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29167,7 +29167,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -40792,7 +40792,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -44071,7 +44071,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47350,7 +47350,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -51784,7 +51784,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -59897,7 +59897,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -63566,7 +63566,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -67230,7 +67230,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -70899,7 +70899,7 @@
       </c>
       <c r="AM370" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN370" t="b">
@@ -74953,7 +74953,7 @@
       </c>
       <c r="AM391" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN391" t="b">
@@ -78232,7 +78232,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -81896,7 +81896,7 @@
       </c>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN427" t="b">
